--- a/PREGAME/1. ELICITACION/1.3 HIstorias de Usuario/G2_Matriz de Marco de Trabajo HU_V2.1_PintaAuto.xlsx
+++ b/PREGAME/1. ELICITACION/1.3 HIstorias de Usuario/G2_Matriz de Marco de Trabajo HU_V2.1_PintaAuto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\22426_G2_ADS\PREGAME\1. ELICITACION\1.3 HIstorias de Usuario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\6TO SEMESTRE\ANALISIS Y DISEÑO DE SOFTWARE\REPOSITORIO\22426_G2_ADS\PREGAME\1. ELICITACION\1.3 HIstorias de Usuario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9977BA1-E6E0-460E-82FE-B474A0AF8AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711C0596-F8F8-4400-846E-E0C2FF9F7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato descripción HU" sheetId="1" r:id="rId1"/>
@@ -548,7 +548,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -809,11 +809,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -888,6 +903,36 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -896,13 +941,20 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -929,41 +981,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -988,6 +1016,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -997,37 +1031,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1399,22 +1417,22 @@
       <c r="L2" s="16"/>
     </row>
     <row r="3" spans="2:16" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="36"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="46"/>
     </row>
     <row r="4" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I4" s="16"/>
@@ -1467,443 +1485,443 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="83" t="s">
+      <c r="G6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="83">
+      <c r="I6" s="34">
         <v>2</v>
       </c>
-      <c r="J6" s="84">
+      <c r="J6" s="35">
         <v>45444</v>
       </c>
-      <c r="K6" s="83" t="s">
+      <c r="K6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="83" t="s">
+      <c r="L6" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="85" t="s">
+      <c r="M6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="83" t="s">
+      <c r="N6" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="83" t="s">
+      <c r="O6" s="34" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="83" t="s">
+      <c r="D7" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="83" t="s">
+      <c r="E7" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="83" t="s">
+      <c r="G7" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="H7" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="83">
+      <c r="I7" s="34">
         <v>3</v>
       </c>
-      <c r="J7" s="84">
+      <c r="J7" s="35">
         <v>45445</v>
       </c>
-      <c r="K7" s="83" t="s">
+      <c r="K7" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="83" t="s">
+      <c r="L7" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="85" t="s">
+      <c r="M7" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="N7" s="83" t="s">
+      <c r="N7" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="O7" s="83" t="s">
+      <c r="O7" s="34" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="83" t="s">
+      <c r="D8" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="83" t="s">
+      <c r="F8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="83" t="s">
+      <c r="G8" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="83" t="s">
+      <c r="H8" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="34">
         <v>3</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="35">
         <v>45446</v>
       </c>
-      <c r="K8" s="83" t="s">
+      <c r="K8" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="83" t="s">
+      <c r="L8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="85" t="s">
+      <c r="M8" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="N8" s="83" t="s">
+      <c r="N8" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="O8" s="83" t="s">
+      <c r="O8" s="34" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="83" t="s">
+      <c r="F9" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="87" t="s">
+      <c r="G9" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="83" t="s">
+      <c r="H9" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="83">
+      <c r="I9" s="34">
         <v>3</v>
       </c>
-      <c r="J9" s="84">
+      <c r="J9" s="35">
         <v>45447</v>
       </c>
-      <c r="K9" s="83" t="s">
+      <c r="K9" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="83" t="s">
+      <c r="L9" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="83" t="s">
+      <c r="M9" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="83" t="s">
+      <c r="N9" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="88" t="s">
+      <c r="O9" s="39" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="34">
+        <v>2</v>
+      </c>
+      <c r="J10" s="35">
+        <v>45449</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="N10" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="O10" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="P10" s="33"/>
+    </row>
+    <row r="11" spans="2:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="87" t="s">
+      <c r="D11" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E11" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="83" t="s">
+      <c r="F11" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="87" t="s">
+      <c r="G11" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="83" t="s">
+      <c r="H11" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="83">
+      <c r="I11" s="34">
+        <v>4</v>
+      </c>
+      <c r="J11" s="35">
+        <v>45449</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="93" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="34">
+        <v>4</v>
+      </c>
+      <c r="J12" s="35">
+        <v>45451</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12" s="34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="34">
+        <v>2</v>
+      </c>
+      <c r="J13" s="35">
+        <v>45449</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="34">
         <v>3</v>
       </c>
-      <c r="J10" s="84">
-        <v>45448</v>
-      </c>
-      <c r="K10" s="83" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="83" t="s">
+      <c r="J14" s="35">
+        <v>45451</v>
+      </c>
+      <c r="K14" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="89" t="s">
+      <c r="M14" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="O10" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="P10" s="33"/>
-    </row>
-    <row r="11" spans="2:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="87" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="83" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="83" t="s">
+      <c r="O14" s="34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="91" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="83" t="s">
+      <c r="G15" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="83">
+      <c r="I15" s="34">
         <v>3</v>
       </c>
-      <c r="J11" s="84">
-        <v>45450</v>
-      </c>
-      <c r="K11" s="83" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="83" t="s">
+      <c r="J15" s="35">
+        <v>45452</v>
+      </c>
+      <c r="K15" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="N11" s="83" t="s">
-        <v>74</v>
-      </c>
-      <c r="O11" s="83" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="83" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="83" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="83" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" s="83" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="83">
-        <v>2</v>
-      </c>
-      <c r="J12" s="84">
-        <v>45449</v>
-      </c>
-      <c r="K12" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="N12" s="83" t="s">
-        <v>109</v>
-      </c>
-      <c r="O12" s="92" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="86" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="83" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="83" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="83">
-        <v>2</v>
-      </c>
-      <c r="J13" s="84">
-        <v>45449</v>
-      </c>
-      <c r="K13" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="N13" s="83" t="s">
+      <c r="M15" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="N15" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="O13" s="92" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" ht="51" x14ac:dyDescent="0.3">
-      <c r="B14" s="83" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="91" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="83">
-        <v>3</v>
-      </c>
-      <c r="J14" s="84">
-        <v>45451</v>
-      </c>
-      <c r="K14" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="83" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14" s="83" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="83" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="91" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="91" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="83">
-        <v>3</v>
-      </c>
-      <c r="J15" s="84">
-        <v>45452</v>
-      </c>
-      <c r="K15" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="L15" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="N15" s="83" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="83" t="s">
+      <c r="O15" s="34" t="s">
         <v>88</v>
       </c>
     </row>
@@ -7826,7 +7844,7 @@
     <mergeCell ref="B3:O3"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="L6:L10">
+  <conditionalFormatting sqref="L6:L9 L11">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7836,7 +7854,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11:L15">
+  <conditionalFormatting sqref="L12:L15 L10">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -7893,23 +7911,23 @@
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="56"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="3"/>
@@ -7949,15 +7967,15 @@
         <v>1</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="55" t="s">
+      <c r="E9" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="56"/>
+      <c r="F9" s="68"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="56"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -7972,17 +7990,17 @@
         <v>83</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="57" t="str">
+      <c r="E10" s="70" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,5,0)</f>
         <v>Propietario</v>
       </c>
-      <c r="F10" s="56"/>
+      <c r="F10" s="68"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="57" t="str">
+      <c r="H10" s="70" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,11,0)</f>
         <v>No iniciado</v>
       </c>
-      <c r="I10" s="56"/>
+      <c r="I10" s="68"/>
       <c r="J10" s="9"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -8014,15 +8032,15 @@
         <v>95</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="56"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="55" t="s">
+      <c r="H12" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="56"/>
+      <c r="I12" s="68"/>
       <c r="J12" s="9"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -8038,17 +8056,17 @@
         <v>3</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="57" t="str">
+      <c r="E13" s="70" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,10,0)</f>
         <v xml:space="preserve">Media </v>
       </c>
-      <c r="F13" s="56"/>
+      <c r="F13" s="68"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="57" t="str">
+      <c r="H13" s="70" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,7,0)</f>
         <v>Gabriel Reinoso</v>
       </c>
-      <c r="I13" s="56"/>
+      <c r="I13" s="68"/>
       <c r="J13" s="9"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -8076,68 +8094,68 @@
     </row>
     <row r="15" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="31"/>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="74" t="str">
+      <c r="D15" s="75" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,3,0)</f>
         <v>Generar reporte en fechas especificas</v>
       </c>
-      <c r="E15" s="75"/>
+      <c r="E15" s="76"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="74" t="str">
+      <c r="H15" s="75" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,4,0)</f>
         <v>Para que tenga una visión clara del inventario durante una fecha especifica</v>
       </c>
-      <c r="I15" s="80"/>
-      <c r="J15" s="75"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="76"/>
       <c r="K15" s="25"/>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="M15" s="40" t="str">
+      <c r="M15" s="86" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,6,0)</f>
         <v>Selecciona la opcion de generar reportes, ingresa la fecha de la cual quiere el reporte</v>
       </c>
-      <c r="N15" s="41"/>
-      <c r="O15" s="42"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="59"/>
       <c r="P15" s="32"/>
     </row>
     <row r="16" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="31"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="77"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="78"/>
       <c r="F16" s="25"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="77"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="78"/>
       <c r="K16" s="25"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="45"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="62"/>
       <c r="P16" s="32"/>
     </row>
     <row r="17" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="31"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="79"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="80"/>
       <c r="K17" s="25"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="48"/>
+      <c r="L17" s="82"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="65"/>
       <c r="P17" s="32"/>
     </row>
     <row r="18" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8159,41 +8177,41 @@
     </row>
     <row r="19" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="31"/>
-      <c r="C19" s="60" t="s">
+      <c r="C19" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="61"/>
-      <c r="E19" s="49" t="str">
+      <c r="D19" s="51"/>
+      <c r="E19" s="87" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,14,0)</f>
         <v>Generar reportes por fechas</v>
       </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="51"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="89"/>
       <c r="P19" s="32"/>
     </row>
     <row r="20" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="31"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="54"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="92"/>
       <c r="P20" s="32"/>
     </row>
     <row r="21" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8215,63 +8233,63 @@
     </row>
     <row r="22" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="31"/>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="61"/>
-      <c r="E22" s="67" t="str">
+      <c r="D22" s="51"/>
+      <c r="E22" s="57" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,12,0)</f>
         <v>El aplicativo muestra el reporte de la fecha seleccionada</v>
       </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="42"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="59"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="64" t="s">
+      <c r="J22" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="61"/>
-      <c r="L22" s="70" t="str">
+      <c r="K22" s="51"/>
+      <c r="L22" s="71" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,13,0)</f>
         <v>N/A</v>
       </c>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="61"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="51"/>
       <c r="P22" s="32"/>
     </row>
     <row r="23" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="31"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="62"/>
       <c r="I23" s="6"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="66"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="56"/>
       <c r="P23" s="32"/>
     </row>
     <row r="24" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="31"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="48"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="65"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="62"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="73"/>
-      <c r="O24" s="63"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="53"/>
       <c r="P24" s="32"/>
     </row>
     <row r="25" spans="2:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9288,6 +9306,11 @@
     <row r="1020" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:O17"/>
+    <mergeCell ref="E19:O20"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C19:D20"/>
     <mergeCell ref="C22:D24"/>
@@ -9304,11 +9327,6 @@
     <mergeCell ref="D15:E17"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="H15:J17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:O17"/>
-    <mergeCell ref="E19:O20"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I11">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -9344,23 +9362,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f1f31ffb-9912-4459-99c8-b26e82094b51" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100EDB39E34F5A9B445B025C05B2A05D030" ma:contentTypeVersion="9" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="c886da2bbaf859996bda4f5adc7dc4d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f1f31ffb-9912-4459-99c8-b26e82094b51" xmlns:ns4="ce621958-37b1-43fe-a1f1-1aad67996a88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bf2d7515a9e37adedddfec1670a2bd68" ns3:_="" ns4:_="">
     <xsd:import namespace="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
@@ -9555,25 +9556,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B92EABA-029D-4E15-9CAD-35D85D8AFEB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f1f31ffb-9912-4459-99c8-b26e82094b51" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BB9B8E-F37C-4883-BB4F-987669CAAE30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E2F3D1-C235-4C14-B824-1A8C3F52885C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9590,4 +9590,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BB9B8E-F37C-4883-BB4F-987669CAAE30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B92EABA-029D-4E15-9CAD-35D85D8AFEB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>